--- a/docs/kịch bản kiểm tra hệ thống Trạng Nguyên_1.xlsx
+++ b/docs/kịch bản kiểm tra hệ thống Trạng Nguyên_1.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30520"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E552B74D-88D0-4987-BA01-D977EEB0F896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Kịch bản kiểm tra" sheetId="1" r:id="rId1"/>
     <sheet name="Webuser các V - Test case" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="223">
   <si>
     <t>STT</t>
   </si>
@@ -713,6 +709,9 @@
     <t>Luồng chuyển V6 → V5 (vào màn Thi hay)</t>
   </si>
   <si>
+    <t>Đã đăng nhập V6 và V5</t>
+  </si>
+  <si>
     <t>1. Click mục 'Thi Toán' trên menu V6 → chờ trang /thi-toan tải xong
 2. Click 1 tab kỳ thi (vd 'Thi VNMF (Lớp 1 - 2 - 3)')
 3. Cuộn xuống bảng chặng thi
@@ -867,57 +866,221 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F4E79"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF595959"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF595959"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF595959"/>
-      <name val="Times New Roman"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -926,136 +1089,239 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC55A11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC55A11"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="20">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1110,166 +1376,535 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1318,7 +1953,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1351,26 +1986,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1403,23 +2021,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1561,354 +2162,349 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A3:K17"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="27.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32" style="3" customWidth="1"/>
-    <col min="5" max="5" width="32.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="34.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="29.42578125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="35.85546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="3"/>
-    <col min="11" max="11" width="38.7109375" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="9.14285714285714" style="17"/>
+    <col min="2" max="2" width="27.5714285714286" style="18" customWidth="1"/>
+    <col min="3" max="3" width="36.7142857142857" style="18" customWidth="1"/>
+    <col min="4" max="4" width="32" style="18" customWidth="1"/>
+    <col min="5" max="5" width="32.8571428571429" style="18" customWidth="1"/>
+    <col min="6" max="6" width="34.7142857142857" style="18" customWidth="1"/>
+    <col min="7" max="7" width="29.4285714285714" style="18" customWidth="1"/>
+    <col min="8" max="8" width="35.8571428571429" style="17" customWidth="1"/>
+    <col min="9" max="9" width="11.7142857142857" style="17" customWidth="1"/>
+    <col min="10" max="10" width="9.14285714285714" style="18"/>
+    <col min="11" max="11" width="38.7142857142857" style="18" customWidth="1"/>
+    <col min="12" max="16384" width="9.14285714285714" style="18"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="19.5" customHeight="1">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="5" spans="1:11" ht="51" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="3" ht="19.5" customHeight="1" spans="1:11">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+    </row>
+    <row r="5" ht="51" customHeight="1" spans="1:11">
+      <c r="A5" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="29" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="61.5">
-      <c r="A6" s="11">
+    <row r="6" ht="63" spans="1:11">
+      <c r="A6" s="30">
         <v>1</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="11" t="s">
+      <c r="H6" s="36"/>
+      <c r="I6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="37" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30.75">
-      <c r="A7" s="11">
+    <row r="7" ht="31.5" spans="1:11">
+      <c r="A7" s="30">
         <v>2</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="11" t="s">
+      <c r="H7" s="36"/>
+      <c r="I7" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="73.5" customHeight="1">
-      <c r="A8" s="11">
+    <row r="8" ht="73.5" customHeight="1" spans="1:11">
+      <c r="A8" s="30">
         <v>3</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="91.5">
-      <c r="A9" s="11">
+    <row r="9" ht="94.5" spans="1:11">
+      <c r="A9" s="30">
         <v>4</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28" t="s">
+      <c r="E9" s="42"/>
+      <c r="F9" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="119.25" customHeight="1">
-      <c r="A10" s="11">
+    <row r="10" ht="119.25" customHeight="1" spans="1:11">
+      <c r="A10" s="30">
         <v>5</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="44"/>
+      <c r="C10" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="19" t="s">
+      <c r="E10" s="38"/>
+      <c r="F10" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="26" t="s">
+      <c r="G10" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="103.5" customHeight="1">
-      <c r="A11" s="11">
+    <row r="11" ht="103.5" customHeight="1" spans="1:11">
+      <c r="A11" s="30">
         <v>6</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="26" t="s">
+      <c r="G11" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="30" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="I12" s="11"/>
+      <c r="I12" s="30"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="1:11" ht="40.5" customHeight="1">
-      <c r="A14" s="11" t="s">
+      <c r="I13" s="30"/>
+    </row>
+    <row r="14" ht="40.5" customHeight="1" spans="1:11">
+      <c r="A14" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="K14" s="10" t="s">
+      <c r="I14" s="20"/>
+      <c r="K14" s="29" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="76.5" customHeight="1">
-      <c r="A15" s="11">
+    <row r="15" ht="76.5" customHeight="1" spans="1:11">
+      <c r="A15" s="30">
         <v>1</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G15" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="11" t="s">
+      <c r="H15" s="36"/>
+      <c r="I15" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="37" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="35.25" customHeight="1">
-      <c r="A16" s="11">
+    <row r="16" ht="35.25" customHeight="1" spans="1:11">
+      <c r="A16" s="30">
         <v>2</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="11" t="s">
+      <c r="H16" s="36"/>
+      <c r="I16" s="30" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A17" s="11">
+    <row r="17" ht="28.5" customHeight="1" spans="1:9">
+      <c r="A17" s="30">
         <v>3</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="26"/>
-      <c r="I17" s="11" t="s">
+      <c r="H17" s="36"/>
+      <c r="I17" s="30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1917,918 +2513,920 @@
     <mergeCell ref="B9:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725696CC-6BC1-42CE-BFE2-CB0ABD653820}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="27.42578125" customWidth="1"/>
-    <col min="6" max="6" width="70.42578125" customWidth="1"/>
-    <col min="7" max="7" width="55.85546875" customWidth="1"/>
-    <col min="8" max="8" width="33.7109375" customWidth="1"/>
-    <col min="9" max="9" width="47.42578125" customWidth="1"/>
-    <col min="10" max="10" width="50.7109375" customWidth="1"/>
-    <col min="11" max="11" width="48.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="12.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="32.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="11.7142857142857" customWidth="1"/>
+    <col min="5" max="5" width="27.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="70.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="55.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="33.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="47.4285714285714" customWidth="1"/>
+    <col min="10" max="10" width="50.7142857142857" customWidth="1"/>
+    <col min="11" max="11" width="48.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="34" customFormat="1" ht="36" customHeight="1">
-      <c r="A1" s="43" t="s">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:11">
+      <c r="A1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-    </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:11">
+      <c r="A2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="24" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:11">
+      <c r="A3" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-    </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1">
-      <c r="A4" s="33" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:11">
+      <c r="A4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-    </row>
-    <row r="5" spans="1:11" ht="24" customHeight="1">
-      <c r="A5" s="33" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:11">
+      <c r="A5" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-    </row>
-    <row r="6" spans="1:11" ht="24" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:11">
+      <c r="A6" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-    </row>
-    <row r="7" spans="1:11" ht="24" customHeight="1">
-      <c r="A7" s="33" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-    </row>
-    <row r="8" spans="1:11" ht="24" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:11">
+      <c r="A8" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11" ht="24" customHeight="1">
-      <c r="A9" s="50" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:11">
+      <c r="A9" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-    </row>
-    <row r="11" spans="1:11" s="37" customFormat="1" ht="36.75" customHeight="1">
-      <c r="A11" s="35" t="s">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+    </row>
+    <row r="10" ht="15.75" spans="1:11">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
+      <c r="A11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="35" t="s">
+      <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="36" t="s">
+      <c r="J11" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="K11" s="35" t="s">
+      <c r="K11" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="45" t="s">
+    <row r="12" s="1" customFormat="1" ht="21" customHeight="1" spans="1:11">
+      <c r="A12" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
-      <c r="K12" s="47"/>
-    </row>
-    <row r="13" spans="1:11" s="42" customFormat="1" ht="137.25" customHeight="1">
-      <c r="A13" s="38" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" s="3" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
+      <c r="A13" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="I13" s="40" t="s">
+      <c r="I13" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="K13" s="15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="42" customFormat="1" ht="137.25" customHeight="1">
-      <c r="A14" s="38" t="s">
+    <row r="14" s="3" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
+      <c r="A14" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I14" s="40" t="s">
+      <c r="I14" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="J14" s="41" t="s">
+      <c r="J14" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="42" customFormat="1" ht="137.25" customHeight="1">
-      <c r="A15" s="38" t="s">
+    <row r="15" s="3" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
+      <c r="A15" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="41" t="s">
+      <c r="J15" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="K15" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="42" customFormat="1" ht="92.25" customHeight="1">
-      <c r="A16" s="38" t="s">
+    <row r="16" s="3" customFormat="1" ht="92.25" customHeight="1" spans="1:11">
+      <c r="A16" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="41" t="s">
+      <c r="J16" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="39" t="s">
+      <c r="K16" s="15" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="42" customFormat="1" ht="67.5" customHeight="1">
-      <c r="A17" s="38" t="s">
+    <row r="17" s="3" customFormat="1" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A17" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="D17" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E17" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="40" t="s">
+      <c r="H17" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I17" s="40" t="s">
+      <c r="I17" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="41" t="s">
+      <c r="J17" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="42" customFormat="1" ht="68.25" customHeight="1">
-      <c r="A18" s="38" t="s">
+    <row r="18" s="3" customFormat="1" ht="68.25" customHeight="1" spans="1:11">
+      <c r="A18" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="E18" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I18" s="40" t="s">
+      <c r="I18" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="41" t="s">
+      <c r="J18" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="39" t="s">
+      <c r="K18" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="42" customFormat="1" ht="72" customHeight="1">
-      <c r="A19" s="38" t="s">
+    <row r="19" s="3" customFormat="1" ht="72" customHeight="1" spans="1:11">
+      <c r="A19" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="39" t="s">
+      <c r="E19" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="41" t="s">
+      <c r="J19" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="15" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="34" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A20" s="45" t="s">
+    <row r="20" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:11">
+      <c r="A20" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="47"/>
-    </row>
-    <row r="21" spans="1:11" s="42" customFormat="1" ht="107.25">
-      <c r="A21" s="38" t="s">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" s="3" customFormat="1" ht="110.25" spans="1:11">
+      <c r="A21" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="39" t="s">
+      <c r="E21" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="H21" s="40" t="s">
+      <c r="H21" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="I21" s="40" t="s">
+      <c r="I21" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="41" t="s">
+      <c r="J21" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="42" customFormat="1" ht="137.25">
-      <c r="A22" s="38" t="s">
+    <row r="22" s="3" customFormat="1" ht="110.25" spans="1:11">
+      <c r="A22" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D22" s="39" t="s">
+      <c r="D22" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E22" s="39" t="s">
+      <c r="E22" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F22" s="39" t="s">
+      <c r="F22" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="40" t="s">
+      <c r="H22" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I22" s="40" t="s">
+      <c r="I22" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="J22" s="41" t="s">
+      <c r="J22" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="K22" s="39" t="s">
+      <c r="K22" s="15" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="42" customFormat="1" ht="91.5">
-      <c r="A23" s="38" t="s">
+    <row r="23" s="3" customFormat="1" ht="94.5" spans="1:11">
+      <c r="A23" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="39" t="s">
+      <c r="D23" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F23" s="39" t="s">
+      <c r="F23" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="G23" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="H23" s="40" t="s">
+      <c r="H23" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I23" s="40" t="s">
+      <c r="I23" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="J23" s="41" t="s">
+      <c r="J23" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="K23" s="39" t="s">
+      <c r="K23" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="42" customFormat="1" ht="107.25">
-      <c r="A24" s="38" t="s">
+    <row r="24" s="3" customFormat="1" ht="110.25" spans="1:11">
+      <c r="A24" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="39" t="s">
+      <c r="E24" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="H24" s="40" t="s">
+      <c r="H24" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I24" s="40" t="s">
+      <c r="I24" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="J24" s="41" t="s">
+      <c r="J24" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="42" customFormat="1" ht="121.5">
-      <c r="A25" s="38" t="s">
+    <row r="25" s="3" customFormat="1" ht="126" spans="1:11">
+      <c r="A25" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="E25" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F25" s="39" t="s">
+      <c r="F25" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="G25" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="H25" s="40" t="s">
+      <c r="H25" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I25" s="40" t="s">
+      <c r="I25" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="J25" s="41" t="s">
+      <c r="J25" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="K25" s="39" t="s">
+      <c r="K25" s="15" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="42" customFormat="1" ht="61.5">
-      <c r="A26" s="38" t="s">
+    <row r="26" s="3" customFormat="1" ht="63" spans="1:11">
+      <c r="A26" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="D26" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="E26" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="39" t="s">
+      <c r="F26" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="G26" s="40" t="s">
+      <c r="G26" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="H26" s="40" t="s">
+      <c r="H26" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I26" s="40" t="s">
+      <c r="I26" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="41" t="s">
+      <c r="J26" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="K26" s="39" t="s">
+      <c r="K26" s="15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="42" customFormat="1" ht="91.5">
-      <c r="A27" s="38" t="s">
+    <row r="27" s="3" customFormat="1" ht="94.5" spans="1:11">
+      <c r="A27" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E27" s="39" t="s">
+      <c r="E27" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="G27" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" s="3" customFormat="1" ht="47.25" spans="1:11">
+      <c r="A28" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F27" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="G27" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="H27" s="40" t="s">
+      <c r="F28" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="H28" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I27" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="J27" s="41" t="s">
-        <v>187</v>
-      </c>
-      <c r="K27" s="39" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="42" customFormat="1" ht="45.75">
-      <c r="A28" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="B28" s="39" t="s">
+      <c r="I28" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" ht="31.5" spans="1:11">
+      <c r="A29" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C28" s="39" t="s">
-        <v>190</v>
-      </c>
-      <c r="D28" s="39" t="s">
+      <c r="C29" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E29" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F28" s="39" t="s">
-        <v>191</v>
-      </c>
-      <c r="G28" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="H28" s="40" t="s">
+      <c r="F29" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="H29" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="I29" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:11">
+      <c r="A30" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="13"/>
+    </row>
+    <row r="31" s="3" customFormat="1" ht="78.75" spans="1:11">
+      <c r="A31" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="H31" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="I28" s="40" t="s">
+      <c r="I31" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" s="3" customFormat="1" ht="63" spans="1:11">
+      <c r="A32" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="G32" s="50" t="s">
+        <v>216</v>
+      </c>
+      <c r="H32" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" s="3" customFormat="1" ht="47.25" spans="1:11">
+      <c r="A33" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="H33" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="J28" s="41" t="s">
-        <v>193</v>
-      </c>
-      <c r="K28" s="39" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="42" customFormat="1" ht="45.75">
-      <c r="A29" s="38" t="s">
+      <c r="J33" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" s="15" t="s">
         <v>195</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>143</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="G29" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="H29" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="I29" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="J29" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="K29" s="39" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="34" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A30" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="47"/>
-    </row>
-    <row r="31" spans="1:11" s="42" customFormat="1" ht="76.5">
-      <c r="A31" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="G31" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="H31" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="I31" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="J31" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="K31" s="39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" s="42" customFormat="1" ht="61.5">
-      <c r="A32" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="E32" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="G32" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="H32" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="I32" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="J32" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="K32" s="39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" s="42" customFormat="1" ht="45.75">
-      <c r="A33" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="B33" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="H33" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="I33" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="J33" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="K33" s="39" t="s">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2838,5 +3436,6 @@
     <mergeCell ref="A30:K30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/docs/kịch bản kiểm tra hệ thống Trạng Nguyên_1.xlsx
+++ b/docs/kịch bản kiểm tra hệ thống Trạng Nguyên_1.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Kịch bản kiểm tra" sheetId="1" r:id="rId1"/>
     <sheet name="Webuser các V - Test case" sheetId="2" r:id="rId2"/>
+    <sheet name="Quản trị các V - Test case" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="322">
+  <si>
+    <t>Webuser</t>
+  </si>
   <si>
     <t>STT</t>
   </si>
@@ -58,6 +62,9 @@
   </si>
   <si>
     <t>Điều kiện</t>
+  </si>
+  <si>
+    <t>Tài khoản chạy test</t>
   </si>
   <si>
     <t>Login</t>
@@ -90,6 +97,9 @@
 - Test fresh session (Không cache)</t>
   </si>
   <si>
+    <t>vnmfthu1/Tne@2526</t>
+  </si>
+  <si>
     <t>Logout</t>
   </si>
   <si>
@@ -105,35 +115,10 @@
 - Thời gian: t&gt; 6s</t>
   </si>
   <si>
-    <t>To do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiển thị </t>
-  </si>
-  <si>
-    <t>- Các menu chính
-- Các button
- (Ưu tiên TNMath)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- Hiển thị các button và click được đúng chức năng </t>
-  </si>
-  <si>
-    <t>- UI load chậm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-- Có &gt;= 1 button không hiển thị/ hiển thị nhưng không click được</t>
-  </si>
-  <si>
-    <t>Chỉ chạy trên TNMath</t>
-  </si>
-  <si>
-    <t>Kiểm tra random</t>
-  </si>
-  <si>
-    <t>Học random 1 bài giảng</t>
+    <t>Kiểm tra random (V2, V6)</t>
+  </si>
+  <si>
+    <t>Xem video 1 bài giảng</t>
   </si>
   <si>
     <t xml:space="preserve">- Video load thành công
@@ -141,21 +126,26 @@
 </t>
   </si>
   <si>
+    <t>- Không áp dụng</t>
+  </si>
+  <si>
     <t>- Video không load được
 - Thời gian phát không tăng</t>
   </si>
   <si>
-    <t>Verify media thì nên manual test, auto chỉ test được tốc độ tải video, tuy nhiên độ dài ngắn video hoặc tốc độ mạng có thể ảnh hưởng tới thời gian load, ngoài ra, video giật lag giữa chừng auto cũng ko check được</t>
-  </si>
-  <si>
-    <t>Làm bài tập/ bài kiểm tra/ bài luyện</t>
-  </si>
-  <si>
-    <t>- Quá trình làm bài xuyên suốt không bị out, user nộp bài thành công, hệ thống tự nộp bài thành công, hệ thống trả về kết quả đúng</t>
-  </si>
-  <si>
-    <t>- Đang làm bài bị out ra/ chọn đáp án Không nhận, Hiển thị hình ảnh Tại câu hỏi bị lỗi/ nộp bài Không được/ hết giờ hệ thống Không tự nộp bài
-- Hoặc kết quả tổng kết bài làm Thời gian ghi nhận Không chính xác/ ghi nhận điểm Không chính xác</t>
+    <t>Làm lần lượt: 
+1 bài tập
+1 bài kiểm tra
+1 bài luyện
+1 bài thi (V6 không check thi)</t>
+  </si>
+  <si>
+    <t>- Đề HIỂN THỊ (có nội dung câu hỏi)
+- Nộp bài THÀNH CÔNG (có thông báo xác nhận)</t>
+  </si>
+  <si>
+    <t>- Đề KHÔNG hiển thị / trang lỗi
+- Nộp bài THẤT BẠI (không có thông báo xác nhận, luyện V5 không check nộp bài do cần check nộp từ câu)</t>
   </si>
   <si>
     <t>Check user hiện đề + nộp bài thành công</t>
@@ -164,8 +154,8 @@
     <t>Luồng chuyển V</t>
   </si>
   <si>
-    <t>- Từ V5 -&gt; V6 (qua button VNMF/banner)
-- Từ V6 -&gt; V5 (qua button Thi ngay)
+    <t>- Từ V5 -&gt; V6 (qua button VNMF)
+- Từ V6 -&gt; V5 (qua button Thi ngay tại màn Học Toán)
 - Từ V6 -&gt; VNMF (qua button VNMF)
 - Từ VNMF -&gt; V6 (qua button Đăng nhập)</t>
   </si>
@@ -178,10 +168,30 @@
 - Flicker UI</t>
   </si>
   <si>
-    <t>- Điều hướng sai/ Không load được/lỗi hiển thị</t>
-  </si>
-  <si>
-    <t>Ko verify flicker UI</t>
+    <t>- Điều hướng SAI trang
+- Trang KHÔNG load được / lỗi hiển thị / HTTP status ≠ 200</t>
+  </si>
+  <si>
+    <t>Ko verify flicker UI, 
+Không đánh giá thời gian.</t>
+  </si>
+  <si>
+    <t>Đấu trường (Chỉ V6)</t>
+  </si>
+  <si>
+    <t>Đấu bot</t>
+  </si>
+  <si>
+    <t>- Màn đấu trường hiển thị câu hỏi</t>
+  </si>
+  <si>
+    <t>- Màn đấu trường KHÔNG hiển thị câu hỏi</t>
+  </si>
+  <si>
+    <t>Check hiện đề</t>
+  </si>
+  <si>
+    <t>Quản trị</t>
   </si>
   <si>
     <t>Vị trí kiểm tra (CMS: V2, V5, V6)</t>
@@ -196,10 +206,14 @@
     <t>Login/ logout</t>
   </si>
   <si>
-    <t>- Cms2
-- Cms5
-- Cms6
-- Quản trị(random 1 tk có role bất kỳ )</t>
+    <t xml:space="preserve"> - CMS2
+- CMS5
+- CMS6
+- Quản trị
+- Nội bộ
+- Cms new
+- Minio 
+- Admin vnmf</t>
   </si>
   <si>
     <t>- Login/Logout bình thườngthường</t>
@@ -211,6 +225,9 @@
   <si>
     <t>- Login/logout fail
 - Login pass &amp; Thời gian (t): t&gt; 6s</t>
+  </si>
+  <si>
+    <t>To do</t>
   </si>
   <si>
     <t>- Check trên network ổn định (wifi bình thường)
@@ -218,31 +235,82 @@
 - Test fresh session (Không cache)</t>
   </si>
   <si>
+    <t>Kiểm tra random</t>
+  </si>
+  <si>
     <t>Các menu chính</t>
   </si>
   <si>
-    <t>- Hiển thị UI đầy đủ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Load UI hơi chậm </t>
-  </si>
-  <si>
-    <t>- Load UI chậm nhiều &gt; 6s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tính năng search </t>
-  </si>
-  <si>
-    <t>Kiểm tra random tại các menu chính</t>
-  </si>
-  <si>
-    <t>- Tính năng search hoạt động tốt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- search chậm </t>
-  </si>
-  <si>
-    <t>- Không search được/ search trả kết quả không đúng</t>
+    <t>- Trang load thành công, không lỗi (HTTP status = 200)</t>
+  </si>
+  <si>
+    <t>- Trang KHÔNG load được / lỗi hiển thị / HTTP status ≠ 200</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Role/Phân quyền</t>
+  </si>
+  <si>
+    <t>Người thực hiện tạo tài khoản</t>
+  </si>
+  <si>
+    <t>- Cms2: https://cms2.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>healthchecktn</t>
+  </si>
+  <si>
+    <t>healthcheck@tn.edu.vn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỹ tạo tài khoản/ Chị Thư gắn quyền </t>
+  </si>
+  <si>
+    <t>- Cms5: https://admin.infra.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>Hạnh</t>
+  </si>
+  <si>
+    <t>- Cms6: https://admin.tnmath.edu.vn/</t>
+  </si>
+  <si>
+    <t>Full quyền</t>
+  </si>
+  <si>
+    <t>Mỹ</t>
+  </si>
+  <si>
+    <t>- Quản trị: https://quantri.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>qltruong1</t>
+  </si>
+  <si>
+    <t>- Nội bộ: https://noibo.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đạt </t>
+  </si>
+  <si>
+    <t>- Cms new: https://cms-news.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>- Minio: https://minio.trangnguyen.edu.vn/minio/ui/login</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - Admin vnmf: vnmf.edu.vn/admin</t>
+  </si>
+  <si>
+    <t>Hưng</t>
   </si>
   <si>
     <t>HEALTH CHECK HÀNG NGÀY – WEBUSER TRẠNG NGUYÊN (AI tự động chạy)</t>
@@ -260,7 +328,7 @@
     <t>TIÊU CHÍ NHÓM CASE LÀM BÀI (bài tập / bài thi / bài kiểm tra / bài luyện, cả V5 và V6): CHỈ đánh giá 2 điểm — (1) đề bài / đề thi / đề luyện CÓ HIỂN THỊ hay không; (2) NỘP BÀI có thành công hay không. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ đếm ngược, tính đúng của điểm chấm, render công thức hay giao diện.</t>
   </si>
   <si>
-    <t>Verdict: PASS · WARNING · FAIL · INCONCLUSIVE (script không kết luận được → người kiểm tra tay). Ô WARNING ghi 'Không áp dụng' nghĩa là case đó không có tầng cảnh báo — chỉ PASS hoặc FAIL.</t>
+    <t>Verdict: PASS · WARNING · FAIL . Ô WARNING ghi 'Không áp dụng' nghĩa là case đó không có tầng cảnh báo — chỉ PASS hoặc FAIL.</t>
   </si>
   <si>
     <t>Điều kiện chạy (Sheet1 gốc, cột Điều kiện): mạng ổn định, KHÔNG bật VPN, fresh session (ẩn danh / xoá cache). Các case chạy tuần tự trong cùng 1 phiên trình duyệt.</t>
@@ -354,7 +422,7 @@
 vd: PASS | t_login = 2.1s | trang chủ V5 đã login | user = Bùi Thị Thư | SBD = 739231826</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 1 – Login, vị trí 'Trực tiếp từ V5'. Đây là 1 trong 2 case duy nhất còn giữ ngưỡng thời gian.</t>
+    <t xml:space="preserve">Login, vị trí 'Trực tiếp từ V5'. </t>
   </si>
   <si>
     <t>HC-V5-02</t>
@@ -379,11 +447,8 @@
 9. Kiểm tra CÓ thông báo nộp bài thành công hay KHÔNG</t>
   </si>
   <si>
-    <t>- Đề thi HIỂN THỊ (có nội dung câu hỏi)
+    <t xml:space="preserve"> - Đề thi HIỂN THỊ (có nội dung câu hỏi)
 - Nộp bài THÀNH CÔNG (có thông báo xác nhận)</t>
-  </si>
-  <si>
-    <t>- Không áp dụng</t>
   </si>
   <si>
     <t>- Đề thi KHÔNG hiển thị / trang lỗi
@@ -394,7 +459,8 @@
 vd: PASS | hiện đề: có | nộp bài: thành công</t>
   </si>
   <si>
-    <t>TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức. (Sheet1 gốc mục 5) Vòng thi CỐ ĐỊNH, không chọn ngẫu nhiên.</t>
+    <t>TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức. 
+Vòng thi CỐ ĐỊNH, không chọn ngẫu nhiên.</t>
   </si>
   <si>
     <t>HC-V5-03</t>
@@ -424,7 +490,7 @@
 - Nộp bài THẤT BẠI (không có thông báo xác nhận)</t>
   </si>
   <si>
-    <t>TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức. (Sheet1 gốc mục 5)</t>
+    <t xml:space="preserve">TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức. </t>
   </si>
   <si>
     <t>HC-V5-04</t>
@@ -455,7 +521,8 @@
 vd: PASS | Học chữ ch-gi-ng | currentTime = 2.8</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 4 – Kiểm tra random. Gốc để TRỐNG ô Warning nên case này chỉ PASS/FAIL. Không đánh giá thời gian. Verify chất lượng phát video vẫn cần người xem (theo Note gốc).</t>
+    <t xml:space="preserve">Sheet1 gốc mục 4 – Kiểm tra random.  
+Không đánh giá thời gian. </t>
   </si>
   <si>
     <t>HC-V5-05</t>
@@ -499,15 +566,13 @@
 - Trang load thành công, không lỗi (HTTP status = 200)</t>
   </si>
   <si>
-    <t>- Điều hướng SAI trang
-- Trang KHÔNG load được / lỗi hiển thị / HTTP status ≠ 200</t>
-  </si>
-  <si>
     <t>Verdict + host_dich + http_status
 vd: PASS | tnmath.edu.vn | 200</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 6 – Luồng chuyển V. Không verify flicker UI (theo Note gốc). Không đánh giá thời gian. Sau bước này V6 CHƯA đăng nhập; việc lấy thông tin đăng nhập kiểm tra ở HC-V6-01.</t>
+    <t xml:space="preserve"> Luồng chuyển V. 
+Không verify flicker UI. Không đánh giá thời gian. 
+Sau bước này V6 CHƯA đăng nhập; việc lấy thông tin đăng nhập kiểm tra ở HC-V6-01.</t>
   </si>
   <si>
     <t>HC-V5-07</t>
@@ -535,7 +600,7 @@
 vd: PASS | t_logout = 1.3s</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 2 – Logout, vị trí 'Trực tiếp từ V5'. Không có trong video.</t>
+    <t xml:space="preserve">Logout, vị trí 'Trực tiếp từ V5'. </t>
   </si>
   <si>
     <t>B. WEB V6 – tnmath.edu.vn</t>
@@ -580,7 +645,7 @@
 vd: PASS | t_login = 1.4s | nhập lại: không | user = Bùi Thị Thư</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 1 – Login. V6 không tự nhận trạng thái đăng nhập, phải bấm 'Đăng nhập' để lấy thông tin từ V5. Case còn giữ ngưỡng thời gian vì thuộc mục Login.</t>
+    <t>Login. V6 không tự nhận trạng thái đăng nhập, phải bấm 'Đăng nhập' để lấy thông tin từ V5. Case còn giữ ngưỡng thời gian vì thuộc mục Login.</t>
   </si>
   <si>
     <t>HC-V6-02</t>
@@ -605,7 +670,9 @@
 vd: PASS | Tuần 16 – Bài toán liên quan đến phép trừ trong phạm vi 10 | currentTime = 2.9</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 4 – Kiểm tra random. Gốc để TRỐNG ô Warning nên case này chỉ PASS/FAIL. Không đánh giá thời gian. Verify chất lượng phát video vẫn cần người xem (theo Note gốc). Trình phát V6 khác V5 nên kiểm tra riêng.</t>
+    <t xml:space="preserve"> Kiểm tra random, 
+Không đánh giá thời gian. 
+Verify chất lượng phát video vẫn cần người xem . </t>
   </si>
   <si>
     <t>HC-V6-03</t>
@@ -630,6 +697,9 @@
   <si>
     <t>- Đề bài tập KHÔNG hiển thị / trang lỗi
 - Nộp bài THẤT BẠI (không có thông báo xác nhận)</t>
+  </si>
+  <si>
+    <t>TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức.</t>
   </si>
   <si>
     <t>HC-V6-04</t>
@@ -672,7 +742,7 @@
 7. Kiểm tra CÓ thông báo nộp bài thành công hay KHÔNG</t>
   </si>
   <si>
-    <t>TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức. (Sheet1 gốc mục 5) Bảng vòng luyện có 2 button: 'Kết quả' và 'Luyện tập' — phải bấm 'Luyện tập'.</t>
+    <t>TIÊU CHÍ: chỉ đánh giá đề có hiển thị + nộp bài có thành công. KHÔNG đánh giá thời gian nộp bài, số câu, đồng hồ, điểm chấm, render công thức. Bảng vòng luyện có 2 button: 'Kết quả' và 'Luyện tập' — phải bấm 'Luyện tập'.</t>
   </si>
   <si>
     <t>HC-V6-06</t>
@@ -690,17 +760,11 @@
 4. Kiểm tra màn đấu trường CÓ hiển thị câu hỏi hay KHÔNG</t>
   </si>
   <si>
-    <t>- Màn đấu trường hiển thị câu hỏi</t>
-  </si>
-  <si>
-    <t>- Màn đấu trường KHÔNG hiển thị câu hỏi</t>
-  </si>
-  <si>
     <t>Verdict + hien_cau_hoi
 vd: PASS | hiện câu hỏi: có</t>
   </si>
   <si>
-    <t>Không có trong Sheet1 gốc, lấy từ luồng thao tác trong video. Chỉ kiểm tra duy nhất: có hiện câu hỏi hay không.</t>
+    <t>Chỉ kiểm tra duy nhất: có hiện câu hỏi hay không.</t>
   </si>
   <si>
     <t>HC-V6-07</t>
@@ -735,7 +799,7 @@
 vd: PASS | thi.trangnguyen.edu.vn | /vao-thi-trang-nguyen-2023/?package_type=TNT | 200 | phiên: còn</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 6 – Luồng chuyển V (V6 → V5 qua button 'Thi ngay'). Video xác nhận: V6 KHÔNG có màn thi riêng — bấm 'Thi ngay' chuyển thẳng sang màn 'Thi hay' của V5, không qua hộp thoại xác nhận. Không verify flicker UI. Không đánh giá thời gian.</t>
+    <t>Không verify flicker UI. Không đánh giá thời gian.</t>
   </si>
   <si>
     <t>HC-V6-08</t>
@@ -757,9 +821,6 @@
 vd: PASS | vnmf.edu.vn | 200</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 6 – Luồng chuyển V. Không verify flicker UI (theo Note gốc). Không đánh giá thời gian.</t>
-  </si>
-  <si>
     <t>HC-V6-09</t>
   </si>
   <si>
@@ -775,7 +836,7 @@
 vd: PASS | t_logout = 1.2s</t>
   </si>
   <si>
-    <t>Sheet1 gốc mục 2 – Logout, vị trí 'Trực tiếp từ V6'. Không có trong video.</t>
+    <t xml:space="preserve"> Logout, vị trí 'Trực tiếp từ V6'. </t>
   </si>
   <si>
     <t>C. VNMF – vnmf.edu.vn</t>
@@ -813,7 +874,7 @@
 vd: PASS | 200 | menu 5/5</t>
   </si>
   <si>
-    <t>Không có trong Sheet1 gốc, lấy từ luồng thao tác trong video. Không đánh giá thời gian.</t>
+    <t>Không đánh giá thời gian.</t>
   </si>
   <si>
     <t>HC-VNMF-02</t>
@@ -861,6 +922,309 @@
   <si>
     <t>- Điều hướng ĐÚNG trang: host đích = tnmath.edu.vn 
 - Trang load thành công, không lỗi (HTTP status = 200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Không verify flicker UI. Không đánh giá thời gian.</t>
+  </si>
+  <si>
+    <t>HEALTH CHECK HÀNG NGÀY – QUẢN TRỊ CÁC V (AI tự động chạy)</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Phạm vi (sheet 'Kịch bản kiểm tra', phần Quản trị): CMS2 · CMS5 · CMS6 · Quản trị · Nội bộ · Cms new · Admin vnmf</t>
+  </si>
+  <si>
+    <t>Mục đích: kiểm tra SỰ SỐNG CÒN của các hệ thống quản trị. Mỗi hệ thống có 3 case TÁCH BẠCH: Đăng nhập → Kiểm tra TẤT CẢ menu chính → Đăng xuất. Ba case chạy nối tiếp trong CÙNG 1 phiên trình duyệt, không đăng nhập lại giữa chừng.</t>
+  </si>
+  <si>
+    <t>NGƯỠNG THỜI GIAN CHỈ ÁP DỤNG CHO CASE ĐĂNG NHẬP VÀ ĐĂNG XUẤT (kịch bản Quản trị mục 1): PASS t ≤ 4s · WARNING 4s &lt; t ≤ 6s · FAIL t &gt; 6s. Case kiểm tra menu chính KHÔNG đánh giá thời gian.</t>
+  </si>
+  <si>
+    <t>- Cms6: https://admin-pre-uat.tnmath.edu.vn/</t>
+  </si>
+  <si>
+    <t>TIÊU CHÍ CASE MENU CHÍNH (kịch bản Quản trị mục 2): duyệt HẾT các menu chính, mỗi mục chỉ đánh giá trang có load thành công hay không (HTTP status = 200, có hiển thị nội dung). Chỉ cần 1 mục lỗi là cả case FAIL. Không kiểm tra dữ liệu, không thao tác thêm.</t>
+  </si>
+  <si>
+    <t>Verdict: PASS · WARNING · FAIL .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ĐIỀU KIỆN CHẠY (kịch bản Quản trị, cột Điều kiện): mạng ổn định · PHẢI BẬT VPN · test fresh session (tab ẩn danh / đã xoá cache).  </t>
+  </si>
+  <si>
+    <t>Tài khoản đăng nhập: lấy từ bảng tài khoản ở cuối sheet 'Kịch bản kiểm tra' (Link / Username / Pass). KHÔNG chép mật khẩu sang sheet này để tránh lệch dữ liệu khi đổi mật khẩu.</t>
+  </si>
+  <si>
+    <t>- Admin vnmf: vnmf.edu.vn/admin</t>
+  </si>
+  <si>
+    <t>Nguồn: bảng tài khoản cuối sheet 'Kịch bản kiểm tra'. Khi đổi mật khẩu nhớ sửa cả 2 nơi.</t>
+  </si>
+  <si>
+    <t>CMS2  –  https://cms2.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>HC-CMS2-01</t>
+  </si>
+  <si>
+    <t>CMS2</t>
+  </si>
+  <si>
+    <t>Đã bật VPN. Trình duyệt ẩn danh, chưa đăng nhập.</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://cms2.trangnguyen.edu.vn/
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>- Đăng nhập thành công, vào được màn hình chính sau đăng nhập
+- t_login ≤ 4s</t>
+  </si>
+  <si>
+    <t>- Đăng nhập thành công nhưng 4s &lt; t_login ≤ 6s
+- Phải tải lại trang mới vào được màn hình chính</t>
+  </si>
+  <si>
+    <t>- Nhập đúng tài khoản và mật khẩu nhưng KHÔNG đăng nhập được
+- Đăng nhập xong không vào được màn hình chính
+- t_login &gt; 6s</t>
+  </si>
+  <si>
+    <t>Verdict + t_login + man_hinh_dich
+vd: PASS | t_login = 2.3s | vào được màn hình chính</t>
+  </si>
+  <si>
+    <t>HC-CMS2-02</t>
+  </si>
+  <si>
+    <t>Kiểm tra TẤT CẢ menu chính</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-CMS2-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>1. Liệt kê TOÀN BỘ mục trên thanh menu chính, ghi tổng số mục
+2. Click lần lượt TỪNG mục menu chính, không bỏ sót mục nào
+3. Với mỗi mục: chờ trang tải xong, ghi HTTP status và kiểm tra trang có hiển thị nội dung hay không
+4. Sau mỗi mục, quay lại để click mục tiếp theo
+5. Ghi lại danh sách các mục menu bị lỗi (nếu có)</t>
+  </si>
+  <si>
+    <t>- TẤT CẢ menu chính đều load thành công, không lỗi
+- HTTP status = 200 ở mọi mục
+- Mọi trang đều có hiển thị nội dung</t>
+  </si>
+  <si>
+    <t>- Có ≥ 1 menu chính KHÔNG load được / lỗi hiển thị
+- Có ≥ 1 menu chính trả HTTP status ≠ 200
+- Có ≥ 1 menu chính ra trang trắng, không có nội dung</t>
+  </si>
+  <si>
+    <t>Verdict + tong_so_menu + so_menu_pass + danh_sach_menu_loi
+vd: PASS | 8 menu | 8/8 pass | menu lỗi: không có
+vd: FAIL | 8 menu | 6/8 pass | menu lỗi: 'Báo cáo' (500), 'Cấu hình' (trang trắng)</t>
+  </si>
+  <si>
+    <t>HC-CMS2-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-CMS2-02).</t>
+  </si>
+  <si>
+    <t>1. Click đăng xuất. Bắt đầu đếm giờ
+2. Chờ quay về màn hình đăng nhập. Dừng giờ → ghi t_logout</t>
+  </si>
+  <si>
+    <t>- Đăng xuất thành công, quay về màn hình đăng nhập
+- t_logout ≤ 4s</t>
+  </si>
+  <si>
+    <t>- Đăng xuất thất bại, vẫn ở trong hệ thống
+- t_logout &gt; 6s</t>
+  </si>
+  <si>
+    <t>Verdict + t_logout
+vd: PASS | t_logout = 1.5s</t>
+  </si>
+  <si>
+    <t>CMS5  –  https://admin.infra.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>HC-CMS5-01</t>
+  </si>
+  <si>
+    <t>CMS5</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://admin.infra.trangnguyen.edu.vn/
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>Chưa cấp tk chạy test</t>
+  </si>
+  <si>
+    <t>HC-CMS5-02</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-CMS5-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>HC-CMS5-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-CMS5-02).</t>
+  </si>
+  <si>
+    <t>CMS6  –  https://admin-pre-uat.tnmath.edu.vn/</t>
+  </si>
+  <si>
+    <t>HC-CMS6-01</t>
+  </si>
+  <si>
+    <t>CMS6</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://admin-pre-uat.tnmath.edu.vn/
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>HC-CMS6-02</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-CMS6-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>HC-CMS6-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-CMS6-02).</t>
+  </si>
+  <si>
+    <t>Quản trị  –  https://quantri.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>HC-QT-01</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://quantri.trangnguyen.edu.vn/
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>HC-QT-02</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-QT-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>HC-QT-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-QT-02).</t>
+  </si>
+  <si>
+    <t>Nội bộ  –  https://noibo.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>HC-NOIBO-01</t>
+  </si>
+  <si>
+    <t>Nội bộ</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://noibo.trangnguyen.edu.vn/
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>HC-NOIBO-02</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-NOIBO-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>HC-NOIBO-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-NOIBO-02).</t>
+  </si>
+  <si>
+    <t>Cms new  –  https://cms-news.trangnguyen.edu.vn/</t>
+  </si>
+  <si>
+    <t>HC-CMSNEW-01</t>
+  </si>
+  <si>
+    <t>Cms new</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://cms-news.trangnguyen.edu.vn/
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>HC-CMSNEW-02</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-CMSNEW-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>HC-CMSNEW-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-CMSNEW-02).</t>
+  </si>
+  <si>
+    <t>Admin vnmf  –  https://vnmf.edu.vn/admin</t>
+  </si>
+  <si>
+    <t>HC-ADMVNMF-01</t>
+  </si>
+  <si>
+    <t>Admin vnmf</t>
+  </si>
+  <si>
+    <t>1. Bật VPN (bắt buộc — hệ thống quản trị chỉ truy cập được qua VPN)
+2. Mở trình duyệt ở chế độ ẩn danh
+3. Mở URL: https://vnmf.edu.vn/admin
+4. Nhập tên đăng nhập và mật khẩu (lấy từ bảng tài khoản cuối sheet 'Kịch bản kiểm tra')
+5. Click button đăng nhập. Bắt đầu đếm giờ
+6. Chờ vào tới màn hình chính sau đăng nhập. Dừng giờ → ghi t_login</t>
+  </si>
+  <si>
+    <t>HC-ADMVNMF-02</t>
+  </si>
+  <si>
+    <t>Đã đăng nhập thành công ở HC-ADMVNMF-01, đang ở màn hình chính.</t>
+  </si>
+  <si>
+    <t>HC-ADMVNMF-03</t>
+  </si>
+  <si>
+    <t>Đang đăng nhập (sau HC-ADMVNMF-02).</t>
   </si>
 </sst>
 </file>
@@ -873,7 +1237,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -883,8 +1247,63 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF833C00"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F4E79"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -909,20 +1328,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -930,17 +1342,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1080,12 +1504,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1113,7 +1543,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1125,7 +1555,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1316,7 +1746,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1392,6 +1822,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -1432,6 +1875,19 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -1441,6 +1897,28 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1560,161 +2038,162 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1722,132 +2201,277 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2168,350 +2792,463 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K17"/>
+  <dimension ref="A3:N30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" style="17"/>
-    <col min="2" max="2" width="27.5714285714286" style="18" customWidth="1"/>
-    <col min="3" max="3" width="36.7142857142857" style="18" customWidth="1"/>
-    <col min="4" max="4" width="32" style="18" customWidth="1"/>
-    <col min="5" max="5" width="32.8571428571429" style="18" customWidth="1"/>
-    <col min="6" max="6" width="34.7142857142857" style="18" customWidth="1"/>
-    <col min="7" max="7" width="29.4285714285714" style="18" customWidth="1"/>
-    <col min="8" max="8" width="35.8571428571429" style="17" customWidth="1"/>
-    <col min="9" max="9" width="11.7142857142857" style="17" customWidth="1"/>
-    <col min="10" max="10" width="9.14285714285714" style="18"/>
-    <col min="11" max="11" width="38.7142857142857" style="18" customWidth="1"/>
-    <col min="12" max="16384" width="9.14285714285714" style="18"/>
+    <col min="1" max="1" width="9.14285714285714" style="42"/>
+    <col min="2" max="2" width="27.5714285714286" style="43" customWidth="1"/>
+    <col min="3" max="3" width="55.5714285714286" style="43" customWidth="1"/>
+    <col min="4" max="4" width="37.7142857142857" style="43" customWidth="1"/>
+    <col min="5" max="5" width="32.8571428571429" style="43" customWidth="1"/>
+    <col min="6" max="6" width="39.7142857142857" style="43" customWidth="1"/>
+    <col min="7" max="7" width="36.7142857142857" style="43" customWidth="1"/>
+    <col min="8" max="8" width="35.8571428571429" style="42" customWidth="1"/>
+    <col min="9" max="9" width="11.7142857142857" style="42" customWidth="1"/>
+    <col min="10" max="10" width="9.14285714285714" style="43"/>
+    <col min="11" max="11" width="38.7142857142857" style="43" customWidth="1"/>
+    <col min="12" max="12" width="25.8571428571429" style="43" customWidth="1"/>
+    <col min="13" max="13" width="19" style="43" customWidth="1"/>
+    <col min="14" max="14" width="20.5714285714286" style="43" customWidth="1"/>
+    <col min="15" max="16384" width="9.14285714285714" style="43"/>
   </cols>
   <sheetData>
-    <row r="3" ht="19.5" customHeight="1" spans="1:11">
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-    </row>
-    <row r="5" ht="51" customHeight="1" spans="1:11">
-      <c r="A5" s="20" t="s">
+    <row r="3" ht="19.5" customHeight="1" spans="1:14">
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="21" t="s">
+    </row>
+    <row r="5" ht="51" customHeight="1" spans="1:14">
+      <c r="A5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="C5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="D5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="E5" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="F5" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="H5" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="I5" s="54" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" ht="63" spans="1:11">
-      <c r="A6" s="30">
+      <c r="K5" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="63" spans="1:14">
+      <c r="A6" s="45">
         <v>1</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="61"/>
+      <c r="I6" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="31.5" spans="1:14">
+      <c r="A7" s="45">
+        <v>2</v>
+      </c>
+      <c r="B7" s="56" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="61"/>
+      <c r="I7" s="45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="63" spans="1:14">
+      <c r="A8" s="45">
+        <v>3</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="68"/>
+      <c r="I8" s="45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" ht="119.25" customHeight="1" spans="1:14">
+      <c r="A9" s="45">
+        <v>4</v>
+      </c>
+      <c r="B9" s="63"/>
+      <c r="C9" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="99" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="70" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="103.5" customHeight="1" spans="1:14">
+      <c r="A10" s="45">
+        <v>5</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="75" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="76" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" ht="103.5" customHeight="1" spans="1:14">
+      <c r="A11" s="45">
+        <v>6</v>
+      </c>
+      <c r="B11" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="98" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="78" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="I12" s="45"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="45"/>
+    </row>
+    <row r="14" ht="40.5" customHeight="1" spans="1:14">
+      <c r="A14" s="79" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="80" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="55"/>
+      <c r="K14" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="37" t="s">
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="81"/>
+    </row>
+    <row r="15" ht="123" customHeight="1" spans="1:14">
+      <c r="A15" s="45">
+        <v>1</v>
+      </c>
+      <c r="B15" s="82" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="61" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" ht="31.5" spans="1:11">
-      <c r="A7" s="30">
+      <c r="H15" s="61"/>
+      <c r="I15" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="69" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="44"/>
+    </row>
+    <row r="16" ht="35.25" customHeight="1" spans="1:14">
+      <c r="A16" s="45">
         <v>2</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" ht="73.5" customHeight="1" spans="1:11">
-      <c r="A8" s="30">
-        <v>3</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" ht="94.5" spans="1:11">
-      <c r="A9" s="30">
-        <v>4</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" ht="119.25" customHeight="1" spans="1:11">
-      <c r="A10" s="30">
-        <v>5</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" ht="103.5" customHeight="1" spans="1:11">
-      <c r="A11" s="30">
-        <v>6</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="I13" s="30"/>
-    </row>
-    <row r="14" ht="40.5" customHeight="1" spans="1:11">
-      <c r="A14" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="20"/>
-      <c r="K14" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" ht="76.5" customHeight="1" spans="1:11">
-      <c r="A15" s="30">
-        <v>1</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" ht="35.25" customHeight="1" spans="1:11">
-      <c r="A16" s="30">
-        <v>2</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="38" t="s">
+      <c r="B16" s="82" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="85" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="84"/>
+      <c r="F16" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="61"/>
+      <c r="I16" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" ht="28.5" customHeight="1" spans="1:9">
-      <c r="A17" s="30">
-        <v>3</v>
-      </c>
-      <c r="B17" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="48" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="38" t="s">
+    </row>
+    <row r="21" ht="28.5" customHeight="1" spans="3:7">
+      <c r="C21" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="D21" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="30" t="s">
-        <v>22</v>
-      </c>
-    </row>
+      <c r="E21" s="86" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="88" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" ht="21.75" customHeight="1" spans="3:7">
+      <c r="C22" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="91" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="89"/>
+      <c r="G22" s="89" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" ht="21.75" customHeight="1" spans="3:7">
+      <c r="C23" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="89"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" ht="21.75" customHeight="1" spans="3:7">
+      <c r="C24" s="89" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="89"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="89" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" ht="21.75" customHeight="1" spans="3:7">
+      <c r="C25" s="89" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="93" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="92">
+        <v>12345678</v>
+      </c>
+      <c r="F25" s="89"/>
+      <c r="G25" s="89" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" ht="21.75" customHeight="1" spans="3:7">
+      <c r="C26" s="89" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="89"/>
+      <c r="E26" s="92"/>
+      <c r="F26" s="89"/>
+      <c r="G26" s="89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" ht="21.75" customHeight="1" spans="3:7">
+      <c r="C27" s="94" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" s="94"/>
+      <c r="E27" s="95"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1" spans="3:7">
+      <c r="C28" s="94" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" s="94"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1" spans="3:7">
+      <c r="C29" s="89" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="89"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B8:B9"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E22" r:id="rId1" display="healthcheck@tn.edu.vn"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -2537,896 +3274,896 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:11">
-      <c r="A1" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="A1" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:11">
-      <c r="A2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="A2" s="39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:11">
-      <c r="A3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="A3" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:11">
-      <c r="A4" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="A4" s="39" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:11">
-      <c r="A5" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
+      <c r="A5" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="40"/>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:11">
-      <c r="A6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
+      <c r="A6" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:11">
-      <c r="A7" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="A7" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:11">
-      <c r="A8" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="A8" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:11">
-      <c r="A9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="A9" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
     </row>
     <row r="10" ht="15.75" spans="1:11">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
-      <c r="A11" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>81</v>
+      <c r="A10" s="40"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="36.75" customHeight="1" spans="1:11">
+      <c r="A11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="21" customHeight="1" spans="1:11">
-      <c r="A12" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
-      <c r="A13" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="I13" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
-      <c r="A14" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="50" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" s="15" t="s">
+      <c r="A12" s="19" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
-      <c r="A15" s="14" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="21"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
+      <c r="A13" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="B13" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="15" t="s">
+      <c r="C13" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="D13" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="E13" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I15" s="50" t="s">
+      <c r="F13" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="K15" s="15" t="s">
+      <c r="G13" s="100" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="92.25" customHeight="1" spans="1:11">
-      <c r="A16" s="14" t="s">
+      <c r="H13" s="100" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="I13" s="100" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="15" t="s">
+      <c r="J13" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="K13" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="G16" s="50" t="s">
+    </row>
+    <row r="14" s="2" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
+      <c r="A14" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" s="50" t="s">
+      <c r="B14" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="D14" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="F14" s="23" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="67.5" customHeight="1" spans="1:11">
-      <c r="A17" s="14" t="s">
+      <c r="G14" s="100" t="s">
         <v>118</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="15" t="s">
+      <c r="H14" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="J14" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="K14" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="50" t="s">
+    </row>
+    <row r="15" s="2" customFormat="1" ht="137.25" customHeight="1" spans="1:11">
+      <c r="A15" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I17" s="50" t="s">
+      <c r="B15" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="16" t="s">
+      <c r="D15" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="F15" s="23" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="68.25" customHeight="1" spans="1:11">
-      <c r="A18" s="14" t="s">
+      <c r="G15" s="100" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="H15" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="100" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F18" s="15" t="s">
+      <c r="J15" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="K15" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="50" t="s">
+    </row>
+    <row r="16" s="2" customFormat="1" ht="92.25" customHeight="1" spans="1:11">
+      <c r="A16" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I18" s="50" t="s">
+      <c r="B16" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="D16" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="F16" s="23" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="72" customHeight="1" spans="1:11">
-      <c r="A19" s="14" t="s">
+      <c r="G16" s="100" t="s">
         <v>133</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="H16" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="100" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="15" t="s">
+      <c r="J16" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="50" t="s">
+      <c r="K16" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="50" t="s">
+    </row>
+    <row r="17" s="2" customFormat="1" ht="67.5" customHeight="1" spans="1:11">
+      <c r="A17" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="B17" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="D17" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="F17" s="23" t="s">
         <v>140</v>
       </c>
+      <c r="G17" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="100" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="80.25" customHeight="1" spans="1:11">
+      <c r="A18" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="100" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="72" customHeight="1" spans="1:11">
+      <c r="A19" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="100" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="100" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:11">
-      <c r="A20" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="13"/>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="110.25" spans="1:11">
-      <c r="A21" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="I21" s="50" t="s">
+      <c r="A20" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="21"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="110.25" spans="1:11">
+      <c r="A21" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="100" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" s="100" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="110.25" spans="1:11">
+      <c r="A22" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="94.5" spans="1:11">
+      <c r="A23" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="G23" s="100" t="s">
+        <v>180</v>
+      </c>
+      <c r="H23" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="100" t="s">
+        <v>181</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="K23" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="110.25" spans="1:11">
+      <c r="A24" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="G24" s="100" t="s">
+        <v>186</v>
+      </c>
+      <c r="H24" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="100" t="s">
+        <v>187</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="K24" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="126" spans="1:11">
+      <c r="A25" s="22" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="G25" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="H25" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="100" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="63" spans="1:11">
+      <c r="A26" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" s="100" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="94.5" spans="1:11">
+      <c r="A27" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="G27" s="100" t="s">
+        <v>203</v>
+      </c>
+      <c r="H27" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="100" t="s">
+        <v>204</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="47.25" spans="1:11">
+      <c r="A28" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="G28" s="100" t="s">
+        <v>210</v>
+      </c>
+      <c r="H28" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="31.5" spans="1:11">
+      <c r="A29" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="G29" s="100" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="100" t="s">
+        <v>156</v>
+      </c>
+      <c r="J29" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:11">
+      <c r="A30" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="21"/>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="78.75" spans="1:11">
+      <c r="A31" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="G31" s="100" t="s">
+        <v>223</v>
+      </c>
+      <c r="H31" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="100" t="s">
+        <v>224</v>
+      </c>
+      <c r="J31" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="K31" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="63" spans="1:11">
+      <c r="A32" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="G32" s="100" t="s">
+        <v>232</v>
+      </c>
+      <c r="H32" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="100" t="s">
+        <v>233</v>
+      </c>
+      <c r="J32" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="K32" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="47.25" spans="1:11">
+      <c r="A33" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="G33" s="100" t="s">
+        <v>238</v>
+      </c>
+      <c r="H33" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="100" t="s">
+        <v>38</v>
+      </c>
+      <c r="J33" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="110.25" spans="1:11">
-      <c r="A22" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="H22" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I22" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="94.5" spans="1:11">
-      <c r="A23" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>163</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" ht="110.25" spans="1:11">
-      <c r="A24" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="G24" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" ht="126" spans="1:11">
-      <c r="A25" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="G25" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" s="3" customFormat="1" ht="63" spans="1:11">
-      <c r="A26" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="G26" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="H26" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" ht="94.5" spans="1:11">
-      <c r="A27" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="G27" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I27" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" ht="47.25" spans="1:11">
-      <c r="A28" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="G28" s="50" t="s">
-        <v>193</v>
-      </c>
-      <c r="H28" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" ht="31.5" spans="1:11">
-      <c r="A29" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="G29" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="H29" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="I29" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:11">
-      <c r="A30" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="13"/>
-    </row>
-    <row r="31" s="3" customFormat="1" ht="78.75" spans="1:11">
-      <c r="A31" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="G31" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" s="3" customFormat="1" ht="63" spans="1:11">
-      <c r="A32" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="G32" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="H32" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I32" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" ht="47.25" spans="1:11">
-      <c r="A33" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="G33" s="50" t="s">
-        <v>222</v>
-      </c>
-      <c r="H33" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>195</v>
+      <c r="K33" s="23" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3438,4 +4175,1236 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="10.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="24.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="9.57142857142857" customWidth="1"/>
+    <col min="5" max="5" width="34.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="72.5714285714286" customWidth="1"/>
+    <col min="7" max="8" width="36.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="49.1428571428571" customWidth="1"/>
+    <col min="10" max="10" width="44.7142857142857" customWidth="1"/>
+    <col min="11" max="11" width="27.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="48.1428571428571" customWidth="1"/>
+    <col min="14" max="15" width="26.4285714285714" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:15">
+      <c r="A1" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A2" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A3" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="101" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A4" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="101" t="s">
+        <v>245</v>
+      </c>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A5" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="101" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" s="10">
+        <v>12345678</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A6" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="101" t="s">
+        <v>76</v>
+      </c>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="18.75" customHeight="1" spans="1:15">
+      <c r="A7" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:15">
+      <c r="A8" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="21" customHeight="1" spans="1:15">
+      <c r="A9" s="14"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="102" t="s">
+        <v>250</v>
+      </c>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="15.75" spans="1:15">
+      <c r="A11" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="27" customHeight="1" spans="1:15">
+      <c r="A12" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A13" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="G13" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H13" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I13" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K13" s="23"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+    </row>
+    <row r="14" s="4" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A14" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>263</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="H14" s="103" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="103" t="s">
+        <v>266</v>
+      </c>
+      <c r="J14" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+    </row>
+    <row r="15" s="4" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A15" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="G15" s="103" t="s">
+        <v>271</v>
+      </c>
+      <c r="H15" s="103" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="103" t="s">
+        <v>272</v>
+      </c>
+      <c r="J15" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="K15" s="26"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="27" customHeight="1" spans="1:15">
+      <c r="A16" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A17" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I17" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A18" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G18" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H18" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K18" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A19" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G19" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="H19" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="100" t="s">
+        <v>272</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K19" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:15">
+      <c r="A20" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A21" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="G21" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H21" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I21" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K21" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A22" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G22" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H22" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K22" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A23" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G23" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="H23" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="100" t="s">
+        <v>272</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K23" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="27" customHeight="1" spans="1:15">
+      <c r="A24" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A25" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="G25" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H25" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I25" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K25" s="23"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A26" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G26" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H26" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K26" s="23"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A27" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G27" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="H27" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I27" s="100" t="s">
+        <v>272</v>
+      </c>
+      <c r="J27" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K27" s="23"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:15">
+      <c r="A28" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A29" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="G29" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H29" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I29" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J29" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K29" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A30" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G30" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H30" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="J30" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K30" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A31" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="F31" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="G31" s="104" t="s">
+        <v>271</v>
+      </c>
+      <c r="H31" s="104" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="104" t="s">
+        <v>272</v>
+      </c>
+      <c r="J31" s="35" t="s">
+        <v>273</v>
+      </c>
+      <c r="K31" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="27.75" customHeight="1" spans="1:15">
+      <c r="A32" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A33" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="G33" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H33" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I33" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J33" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K33" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A34" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H34" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="J34" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A35" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G35" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="H35" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I35" s="100" t="s">
+        <v>272</v>
+      </c>
+      <c r="J35" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K35" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="26.25" customHeight="1" spans="1:15">
+      <c r="A36" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+    </row>
+    <row r="37" s="2" customFormat="1" ht="110.25" spans="1:15">
+      <c r="A37" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="G37" s="100" t="s">
+        <v>257</v>
+      </c>
+      <c r="H37" s="100" t="s">
+        <v>258</v>
+      </c>
+      <c r="I37" s="100" t="s">
+        <v>259</v>
+      </c>
+      <c r="J37" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="K37" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+    </row>
+    <row r="38" s="2" customFormat="1" ht="94.5" spans="1:15">
+      <c r="A38" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G38" s="100" t="s">
+        <v>265</v>
+      </c>
+      <c r="H38" s="100" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="K38" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+    </row>
+    <row r="39" s="2" customFormat="1" ht="47.25" spans="1:15">
+      <c r="A39" s="22" t="s">
+        <v>320</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="G39" s="100" t="s">
+        <v>271</v>
+      </c>
+      <c r="H39" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="I39" s="100" t="s">
+        <v>272</v>
+      </c>
+      <c r="J39" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="K39" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A36:K36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
 </file>